--- a/src/main/resources/DDT/OrangeExcel.xlsx
+++ b/src/main/resources/DDT/OrangeExcel.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\shashank\Capgemini_Training\Selenium\Adv_Selenium\selenium-advance\src\main\resources\DDT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE2F13B-0B33-4E5F-B65D-848E68FFFD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663119DE-8D78-4859-9E56-81B48AAA1136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{67D94291-99A9-425F-9BBD-D19135FEB13C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>vacancy</t>
   </si>
@@ -42,16 +43,34 @@
     <t>NumPos</t>
   </si>
   <si>
-    <t>QA Engineer</t>
-  </si>
-  <si>
     <t>XXX</t>
   </si>
   <si>
     <t>A8DCo 4Ys 010Z</t>
   </si>
   <si>
-    <t>Automation Tester</t>
+    <t>fname</t>
+  </si>
+  <si>
+    <t>lname</t>
+  </si>
+  <si>
+    <t>empid</t>
+  </si>
+  <si>
+    <t>sha</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>emp69</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
   </si>
 </sst>
 </file>
@@ -432,19 +451,51 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
       </c>
       <c r="E2">
         <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD63AAF-8723-4629-BDE8-18E21EABF950}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
